--- a/AAII_Financials/Quarterly/ASST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="92">
   <si>
     <t>ASST</t>
   </si>
@@ -656,123 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1500</v>
       </c>
       <c r="G8" s="3">
         <v>1500</v>
@@ -781,19 +785,19 @@
         <v>1500</v>
       </c>
       <c r="I8" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="J8" s="3">
         <v>1000</v>
       </c>
       <c r="K8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="3">
         <v>800</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
-        <v>100</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
@@ -817,13 +821,13 @@
         <v>100</v>
       </c>
       <c r="U8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
+      <c r="W8" s="3">
+        <v>200</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
@@ -831,52 +835,55 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E9" s="3">
         <v>13100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21900</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2000</v>
       </c>
       <c r="H9" s="3">
         <v>2000</v>
       </c>
       <c r="I9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J9" s="3">
         <v>3100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
@@ -902,40 +909,43 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-10300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-6800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-20300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I10" s="3">
         <v>-600</v>
       </c>
-      <c r="H10" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
@@ -946,8 +956,8 @@
       <c r="P10" s="3">
         <v>0</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,8 +1013,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1032,11 +1046,11 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,32 +1159,35 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-52200</v>
+        <v>8700</v>
       </c>
       <c r="E14" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="F14" s="3">
         <v>29000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>140800</v>
       </c>
-      <c r="G14" s="3">
-        <v>2700</v>
-      </c>
       <c r="H14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,8 +1206,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1213,8 +1233,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1237,7 +1260,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,61 +1334,62 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>252400</v>
+      </c>
+      <c r="E17" s="3">
         <v>316400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>197400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49700</v>
       </c>
-      <c r="G17" s="3">
-        <v>5300</v>
-      </c>
       <c r="H17" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="I17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J17" s="3">
         <v>6100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
         <v>1400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
-      </c>
-      <c r="T17" s="3">
-        <v>200</v>
       </c>
       <c r="U17" s="3">
         <v>200</v>
@@ -1370,8 +1397,8 @@
       <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>200</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1379,70 +1406,73 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-249500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-313600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-196200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-48200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H18" s="3">
-        <v>-3900</v>
+        <v>-3700</v>
       </c>
       <c r="I18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5500</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
+      <c r="W18" s="3">
+        <v>0</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
@@ -1450,8 +1480,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,35 +1510,36 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4200</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-23900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>17700</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
         <v>-300</v>
       </c>
       <c r="J20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1521,8 +1555,8 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1539,8 +1573,8 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1548,53 +1582,56 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-317800</v>
+        <v>-248700</v>
       </c>
       <c r="E21" s="3">
+        <v>-313000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-172200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-65800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-3800</v>
-      </c>
       <c r="H21" s="3">
-        <v>-3800</v>
+        <v>-3400</v>
       </c>
       <c r="I21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-4700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5400</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,17 +1656,20 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1663,8 +1703,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1690,70 +1730,73 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-257600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-265900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-201300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-206700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H23" s="3">
-        <v>-6300</v>
+        <v>-8900</v>
       </c>
       <c r="I23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-4100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1761,8 +1804,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1805,8 +1851,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,70 +1952,73 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-257600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-265900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-201300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-206700</v>
       </c>
-      <c r="G26" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H26" s="3">
-        <v>-6300</v>
+        <v>-8900</v>
       </c>
       <c r="I26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J26" s="3">
         <v>-4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -1974,70 +2026,73 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-283800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-279400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-205600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-206700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H27" s="3">
-        <v>-6300</v>
+        <v>-8900</v>
       </c>
       <c r="I27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J27" s="3">
         <v>-4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2045,8 +2100,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,35 +2396,38 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4200</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
+        <v>500</v>
+      </c>
+      <c r="F32" s="3">
         <v>23900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-17700</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>300</v>
       </c>
       <c r="I32" s="3">
         <v>300</v>
       </c>
       <c r="J32" s="3">
+        <v>300</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,8 +2443,8 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2391,8 +2461,8 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2400,70 +2470,73 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-257600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-265900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-201300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-206700</v>
       </c>
-      <c r="G33" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H33" s="3">
-        <v>-6300</v>
+        <v>-8900</v>
       </c>
       <c r="I33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
         <v>0</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2544,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,70 +2618,73 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-257600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-265900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-201300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-206700</v>
       </c>
-      <c r="G35" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H35" s="3">
-        <v>-6300</v>
+        <v>-8900</v>
       </c>
       <c r="I35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2613,84 +2692,90 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,58 +2829,59 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E41" s="3">
         <v>95100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>109100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>12600</v>
       </c>
       <c r="H41" s="3">
         <v>12600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>6200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>2900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2814,17 +2901,20 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E42" s="3">
         <v>50500</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -2835,11 +2925,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>16800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2885,8 +2975,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2899,8 +2992,8 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
-        <v>400</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>400</v>
@@ -2926,11 +3019,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2947,8 +3040,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3000,8 +3096,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3027,32 +3123,35 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1600</v>
       </c>
       <c r="F45" s="3">
         <v>1600</v>
       </c>
       <c r="G45" s="3">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3071,14 +3170,14 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
-        <v>200</v>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>200</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -3098,59 +3197,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>192600</v>
+      </c>
+      <c r="E46" s="3">
         <v>151000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>71800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>114200</v>
-      </c>
-      <c r="G46" s="3">
-        <v>14700</v>
       </c>
       <c r="H46" s="3">
         <v>14700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>23800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
         <v>3000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3213,8 +3318,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3240,46 +3345,49 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="E48" s="3">
         <v>4800</v>
       </c>
       <c r="F48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G48" s="3">
         <v>5000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5100</v>
       </c>
       <c r="H48" s="3">
         <v>5100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>2700</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -3296,8 +3404,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3311,8 +3419,11 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3320,49 +3431,49 @@
         <v>15000</v>
       </c>
       <c r="E49" s="3">
-        <v>400</v>
+        <v>15000</v>
       </c>
       <c r="F49" s="3">
         <v>400</v>
       </c>
       <c r="G49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H49" s="3">
         <v>300</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3">
         <v>100</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,32 +3641,35 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1164900</v>
+      </c>
+      <c r="E52" s="3">
         <v>929500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>668600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>673100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3568,8 +3688,8 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,59 +3789,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1377100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1100300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>745500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>792600</v>
-      </c>
-      <c r="G54" s="3">
-        <v>22400</v>
       </c>
       <c r="H54" s="3">
         <v>22400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>28200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
         <v>3100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,52 +3921,53 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>6400</v>
       </c>
       <c r="H57" s="3">
         <v>6400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3862,8 +3993,11 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3871,13 +4005,13 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
@@ -3891,11 +4025,11 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3907,14 +4041,14 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,22 +4067,25 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>0</v>
@@ -3965,8 +4102,8 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -3983,8 +4120,8 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -4004,46 +4141,49 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E60" s="3">
         <v>13200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>8000</v>
       </c>
       <c r="H60" s="3">
         <v>8000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>3300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
-      </c>
-      <c r="O60" s="3">
-        <v>200</v>
       </c>
       <c r="P60" s="3">
         <v>200</v>
@@ -4054,8 +4194,8 @@
       <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>200</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -4075,32 +4215,35 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E61" s="3">
         <v>13100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3600</v>
-      </c>
-      <c r="G61" s="3">
-        <v>3700</v>
       </c>
       <c r="H61" s="3">
         <v>3700</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -4146,8 +4289,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4190,8 +4336,8 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,46 +4585,49 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E66" s="3">
         <v>26300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>11700</v>
       </c>
       <c r="H66" s="3">
         <v>11700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>4900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>100</v>
-      </c>
-      <c r="O66" s="3">
-        <v>200</v>
       </c>
       <c r="P66" s="3">
         <v>200</v>
@@ -4480,8 +4638,8 @@
       <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
+      <c r="S66" s="3">
+        <v>200</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,22 +4835,25 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>702400</v>
+      </c>
+      <c r="E70" s="3">
         <v>359200</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>148800</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
-        <v>72500</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>72500</v>
@@ -4694,14 +4862,14 @@
         <v>72500</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>72500</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>43600</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,59 +4983,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1037200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-753400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-474100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-268400</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-61800</v>
       </c>
       <c r="H72" s="3">
         <v>-61800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-49100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-5600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,22 +5279,25 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>646200</v>
+      </c>
+      <c r="E76" s="3">
         <v>714800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>582400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>779400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-61800</v>
       </c>
       <c r="H76" s="3">
         <v>-61800</v>
@@ -5119,35 +5305,35 @@
       <c r="I76" s="3">
         <v>-49100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="J76" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>-27600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3">
         <v>2900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>200</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,146 +5427,152 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-257600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-265900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-201300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-206700</v>
       </c>
-      <c r="G81" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H81" s="3">
-        <v>-6300</v>
+        <v>-8900</v>
       </c>
       <c r="I81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
         <v>0</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5385,8 +5580,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5424,7 +5623,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -5432,8 +5631,8 @@
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -5462,8 +5661,8 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,67 +6052,70 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-31000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22100</v>
       </c>
-      <c r="G89" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H89" s="3">
-        <v>-5000</v>
+        <v>-4400</v>
       </c>
       <c r="I89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,52 +6156,53 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,46 +6376,49 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-461600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-123800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-180000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-674700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I94" s="3">
         <v>8200</v>
       </c>
-      <c r="H94" s="3">
-        <v>8200</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>8500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4100</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -6199,8 +6429,8 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6291,8 +6525,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,70 +6774,73 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>520400</v>
+      </c>
+      <c r="E100" s="3">
         <v>182400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>149400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>792800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>28900</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>28900</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>200</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6646,8 +6895,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6673,67 +6922,70 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E102" s="3">
         <v>27600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-41600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>96000</v>
       </c>
-      <c r="G102" s="3">
-        <v>3500</v>
-      </c>
       <c r="H102" s="3">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="I102" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="J102" s="3">
         <v>2400</v>
       </c>
       <c r="K102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
